--- a/templates/ERC000028/metadata_template_ERC000028.xlsx
+++ b/templates/ERC000028/metadata_template_ERC000028.xlsx
@@ -21,7 +21,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$M$1:$M$289</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$N$1:$N$14</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="603">
   <si>
     <t>alias</t>
   </si>
@@ -557,6 +557,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -720,6 +723,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2365,7 +2371,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2409,7 +2415,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2436,7 +2442,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3155,6 +3161,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3176,27 +3192,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3216,122 +3232,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3355,144 +3371,144 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -3518,1495 +3534,1495 @@
   <sheetData>
     <row r="1" spans="11:14">
       <c r="K1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="11:14">
       <c r="K2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="3" spans="11:14">
       <c r="M3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="11:14">
       <c r="M4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="11:14">
       <c r="M5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N5" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="11:14">
       <c r="M6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" spans="11:14">
       <c r="M7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" spans="11:14">
       <c r="M8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N8" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" spans="11:14">
       <c r="M9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N9" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" spans="11:14">
       <c r="M10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N10" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" spans="11:14">
       <c r="M11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" spans="11:14">
       <c r="M12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="13" spans="11:14">
       <c r="M13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N13" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" spans="11:14">
       <c r="M14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N14" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="11:14">
       <c r="M15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="11:14">
       <c r="M16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="13:13">
       <c r="M17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="13:13">
       <c r="M18" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="13:13">
       <c r="M19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="13:13">
       <c r="M20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="13:13">
       <c r="M21" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" spans="13:13">
       <c r="M22" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="13:13">
       <c r="M23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="13:13">
       <c r="M24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="13:13">
       <c r="M25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="13:13">
       <c r="M26" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="13:13">
       <c r="M27" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="13:13">
       <c r="M28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="13:13">
       <c r="M29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="13:13">
       <c r="M30" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="13:13">
       <c r="M31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="13:13">
       <c r="M32" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" spans="13:13">
       <c r="M33" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="13:13">
       <c r="M34" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="13:13">
       <c r="M35" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="13:13">
       <c r="M36" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="13:13">
       <c r="M37" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="13:13">
       <c r="M38" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="13:13">
       <c r="M39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="13:13">
       <c r="M40" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="13:13">
       <c r="M41" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" spans="13:13">
       <c r="M42" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" spans="13:13">
       <c r="M43" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" spans="13:13">
       <c r="M44" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45" spans="13:13">
       <c r="M45" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="13:13">
       <c r="M46" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="13:13">
       <c r="M47" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="13:13">
       <c r="M48" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="49" spans="13:13">
       <c r="M49" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="13:13">
       <c r="M50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="51" spans="13:13">
       <c r="M51" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52" spans="13:13">
       <c r="M52" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="13:13">
       <c r="M53" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="13:13">
       <c r="M54" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="13:13">
       <c r="M55" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="56" spans="13:13">
       <c r="M56" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="13:13">
       <c r="M57" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58" spans="13:13">
       <c r="M58" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="13:13">
       <c r="M59" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="13:13">
       <c r="M60" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="13:13">
       <c r="M61" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="13:13">
       <c r="M62" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="63" spans="13:13">
       <c r="M63" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="64" spans="13:13">
       <c r="M64" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="13:13">
       <c r="M65" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="66" spans="13:13">
       <c r="M66" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="13:13">
       <c r="M67" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="68" spans="13:13">
       <c r="M68" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" spans="13:13">
       <c r="M69" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" spans="13:13">
       <c r="M70" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="13:13">
       <c r="M71" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="72" spans="13:13">
       <c r="M72" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" spans="13:13">
       <c r="M73" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="13:13">
       <c r="M74" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="75" spans="13:13">
       <c r="M75" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="13:13">
       <c r="M76" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="77" spans="13:13">
       <c r="M77" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" spans="13:13">
       <c r="M78" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="13:13">
       <c r="M79" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="80" spans="13:13">
       <c r="M80" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="81" spans="13:13">
       <c r="M81" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="82" spans="13:13">
       <c r="M82" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="13:13">
       <c r="M83" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="13:13">
       <c r="M84" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="13:13">
       <c r="M85" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="86" spans="13:13">
       <c r="M86" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="87" spans="13:13">
       <c r="M87" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="88" spans="13:13">
       <c r="M88" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="13:13">
       <c r="M89" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="13:13">
       <c r="M90" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="13:13">
       <c r="M91" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" spans="13:13">
       <c r="M92" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="93" spans="13:13">
       <c r="M93" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="94" spans="13:13">
       <c r="M94" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="13:13">
       <c r="M95" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="96" spans="13:13">
       <c r="M96" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="13:13">
       <c r="M97" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="13:13">
       <c r="M98" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="13:13">
       <c r="M99" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="13:13">
       <c r="M100" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" spans="13:13">
       <c r="M101" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="102" spans="13:13">
       <c r="M102" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="13:13">
       <c r="M103" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="104" spans="13:13">
       <c r="M104" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="13:13">
       <c r="M105" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="13:13">
       <c r="M106" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="107" spans="13:13">
       <c r="M107" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="108" spans="13:13">
       <c r="M108" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" spans="13:13">
       <c r="M109" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="13:13">
       <c r="M110" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="111" spans="13:13">
       <c r="M111" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" spans="13:13">
       <c r="M112" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="13:13">
       <c r="M113" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="13:13">
       <c r="M114" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="13:13">
       <c r="M115" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" spans="13:13">
       <c r="M116" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="13:13">
       <c r="M117" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="118" spans="13:13">
       <c r="M118" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" spans="13:13">
       <c r="M119" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="120" spans="13:13">
       <c r="M120" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="121" spans="13:13">
       <c r="M121" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="122" spans="13:13">
       <c r="M122" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="123" spans="13:13">
       <c r="M123" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="124" spans="13:13">
       <c r="M124" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="125" spans="13:13">
       <c r="M125" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="126" spans="13:13">
       <c r="M126" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="127" spans="13:13">
       <c r="M127" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="128" spans="13:13">
       <c r="M128" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="129" spans="13:13">
       <c r="M129" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="130" spans="13:13">
       <c r="M130" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="131" spans="13:13">
       <c r="M131" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="132" spans="13:13">
       <c r="M132" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="133" spans="13:13">
       <c r="M133" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="13:13">
       <c r="M134" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="135" spans="13:13">
       <c r="M135" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136" spans="13:13">
       <c r="M136" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="137" spans="13:13">
       <c r="M137" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="138" spans="13:13">
       <c r="M138" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="139" spans="13:13">
       <c r="M139" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="140" spans="13:13">
       <c r="M140" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="141" spans="13:13">
       <c r="M141" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="142" spans="13:13">
       <c r="M142" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="143" spans="13:13">
       <c r="M143" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="144" spans="13:13">
       <c r="M144" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="145" spans="13:13">
       <c r="M145" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="146" spans="13:13">
       <c r="M146" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="147" spans="13:13">
       <c r="M147" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="148" spans="13:13">
       <c r="M148" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="149" spans="13:13">
       <c r="M149" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="150" spans="13:13">
       <c r="M150" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="151" spans="13:13">
       <c r="M151" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="152" spans="13:13">
       <c r="M152" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="153" spans="13:13">
       <c r="M153" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="154" spans="13:13">
       <c r="M154" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="155" spans="13:13">
       <c r="M155" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="156" spans="13:13">
       <c r="M156" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="157" spans="13:13">
       <c r="M157" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="158" spans="13:13">
       <c r="M158" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="159" spans="13:13">
       <c r="M159" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="160" spans="13:13">
       <c r="M160" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="161" spans="13:13">
       <c r="M161" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="162" spans="13:13">
       <c r="M162" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="163" spans="13:13">
       <c r="M163" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="164" spans="13:13">
       <c r="M164" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="165" spans="13:13">
       <c r="M165" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="166" spans="13:13">
       <c r="M166" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="167" spans="13:13">
       <c r="M167" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="168" spans="13:13">
       <c r="M168" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="169" spans="13:13">
       <c r="M169" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="170" spans="13:13">
       <c r="M170" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="171" spans="13:13">
       <c r="M171" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="172" spans="13:13">
       <c r="M172" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="173" spans="13:13">
       <c r="M173" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="174" spans="13:13">
       <c r="M174" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="175" spans="13:13">
       <c r="M175" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="176" spans="13:13">
       <c r="M176" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="177" spans="13:13">
       <c r="M177" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" spans="13:13">
       <c r="M178" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="179" spans="13:13">
       <c r="M179" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="180" spans="13:13">
       <c r="M180" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="181" spans="13:13">
       <c r="M181" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="182" spans="13:13">
       <c r="M182" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="183" spans="13:13">
       <c r="M183" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="184" spans="13:13">
       <c r="M184" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="185" spans="13:13">
       <c r="M185" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="186" spans="13:13">
       <c r="M186" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="187" spans="13:13">
       <c r="M187" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="188" spans="13:13">
       <c r="M188" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="189" spans="13:13">
       <c r="M189" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="190" spans="13:13">
       <c r="M190" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="191" spans="13:13">
       <c r="M191" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="192" spans="13:13">
       <c r="M192" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="193" spans="13:13">
       <c r="M193" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="194" spans="13:13">
       <c r="M194" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="195" spans="13:13">
       <c r="M195" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="196" spans="13:13">
       <c r="M196" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="197" spans="13:13">
       <c r="M197" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="198" spans="13:13">
       <c r="M198" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="199" spans="13:13">
       <c r="M199" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="200" spans="13:13">
       <c r="M200" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="201" spans="13:13">
       <c r="M201" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="202" spans="13:13">
       <c r="M202" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="203" spans="13:13">
       <c r="M203" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="204" spans="13:13">
       <c r="M204" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="205" spans="13:13">
       <c r="M205" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="206" spans="13:13">
       <c r="M206" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="207" spans="13:13">
       <c r="M207" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="208" spans="13:13">
       <c r="M208" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="209" spans="13:13">
       <c r="M209" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="210" spans="13:13">
       <c r="M210" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="211" spans="13:13">
       <c r="M211" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="212" spans="13:13">
       <c r="M212" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="213" spans="13:13">
       <c r="M213" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="214" spans="13:13">
       <c r="M214" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="215" spans="13:13">
       <c r="M215" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="216" spans="13:13">
       <c r="M216" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="217" spans="13:13">
       <c r="M217" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="218" spans="13:13">
       <c r="M218" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="219" spans="13:13">
       <c r="M219" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="220" spans="13:13">
       <c r="M220" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="221" spans="13:13">
       <c r="M221" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="222" spans="13:13">
       <c r="M222" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="223" spans="13:13">
       <c r="M223" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="224" spans="13:13">
       <c r="M224" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="225" spans="13:13">
       <c r="M225" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="226" spans="13:13">
       <c r="M226" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="227" spans="13:13">
       <c r="M227" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="228" spans="13:13">
       <c r="M228" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="229" spans="13:13">
       <c r="M229" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="230" spans="13:13">
       <c r="M230" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="231" spans="13:13">
       <c r="M231" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="232" spans="13:13">
       <c r="M232" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="233" spans="13:13">
       <c r="M233" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="234" spans="13:13">
       <c r="M234" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="235" spans="13:13">
       <c r="M235" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="236" spans="13:13">
       <c r="M236" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="237" spans="13:13">
       <c r="M237" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="238" spans="13:13">
       <c r="M238" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="239" spans="13:13">
       <c r="M239" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="240" spans="13:13">
       <c r="M240" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="241" spans="13:13">
       <c r="M241" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="242" spans="13:13">
       <c r="M242" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="243" spans="13:13">
       <c r="M243" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="244" spans="13:13">
       <c r="M244" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="245" spans="13:13">
       <c r="M245" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="246" spans="13:13">
       <c r="M246" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="247" spans="13:13">
       <c r="M247" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="248" spans="13:13">
       <c r="M248" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="249" spans="13:13">
       <c r="M249" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="250" spans="13:13">
       <c r="M250" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="251" spans="13:13">
       <c r="M251" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="252" spans="13:13">
       <c r="M252" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="253" spans="13:13">
       <c r="M253" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="254" spans="13:13">
       <c r="M254" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="255" spans="13:13">
       <c r="M255" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="256" spans="13:13">
       <c r="M256" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="257" spans="13:13">
       <c r="M257" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="258" spans="13:13">
       <c r="M258" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="259" spans="13:13">
       <c r="M259" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="260" spans="13:13">
       <c r="M260" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="261" spans="13:13">
       <c r="M261" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="262" spans="13:13">
       <c r="M262" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="263" spans="13:13">
       <c r="M263" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="264" spans="13:13">
       <c r="M264" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="265" spans="13:13">
       <c r="M265" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="266" spans="13:13">
       <c r="M266" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="267" spans="13:13">
       <c r="M267" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="268" spans="13:13">
       <c r="M268" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="269" spans="13:13">
       <c r="M269" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="270" spans="13:13">
       <c r="M270" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="271" spans="13:13">
       <c r="M271" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="272" spans="13:13">
       <c r="M272" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="273" spans="13:13">
       <c r="M273" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="274" spans="13:13">
       <c r="M274" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="275" spans="13:13">
       <c r="M275" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="276" spans="13:13">
       <c r="M276" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="277" spans="13:13">
       <c r="M277" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="278" spans="13:13">
       <c r="M278" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="279" spans="13:13">
       <c r="M279" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="280" spans="13:13">
       <c r="M280" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="281" spans="13:13">
       <c r="M281" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="282" spans="13:13">
       <c r="M282" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="283" spans="13:13">
       <c r="M283" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="284" spans="13:13">
       <c r="M284" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="285" spans="13:13">
       <c r="M285" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="286" spans="13:13">
       <c r="M286" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="287" spans="13:13">
       <c r="M287" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="288" spans="13:13">
       <c r="M288" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="289" spans="13:13">
       <c r="M289" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000028/metadata_template_ERC000028.xlsx
+++ b/templates/ERC000028/metadata_template_ERC000028.xlsx
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="environmentalsample">'cv_sample'!$K$1:$K$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$M$1:$M$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$M$1:$M$294</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$N$1:$N$14</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="608">
   <si>
     <t>alias</t>
   </si>
@@ -557,6 +557,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -860,13 +863,13 @@
     <t>(Optional) Name of persons or institute who collected the specimen</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
@@ -1109,9 +1112,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1130,6 +1130,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1331,6 +1334,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1340,9 +1346,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1382,7 +1385,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1451,6 +1454,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1526,6 +1532,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1547,6 +1556,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1592,6 +1604,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1604,6 +1619,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1613,9 +1631,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1640,6 +1655,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1700,12 +1718,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1763,7 +1781,7 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
@@ -1775,7 +1793,7 @@
     <t>healthy</t>
   </si>
   <si>
-    <t>host health state</t>
+    <t>host_health_state</t>
   </si>
   <si>
     <t>(Mandatory) Health status of the host at the time of sample collection.</t>
@@ -1787,7 +1805,7 @@
     <t>(Optional) Scientific name of the laboratory host used to propagate the source organism from which the sample was obtained</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Mandatory) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
@@ -2368,7 +2386,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2412,7 +2430,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2439,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3163,6 +3181,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3184,27 +3207,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3224,122 +3247,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3363,144 +3386,144 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -3521,1500 +3544,1525 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="K1:N289"/>
+  <dimension ref="K1:N294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="11:14">
       <c r="K1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" spans="11:14">
       <c r="K2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3" spans="11:14">
       <c r="M3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N3" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="11:14">
       <c r="M4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" spans="11:14">
       <c r="M5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N5" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" spans="11:14">
       <c r="M6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N6" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" spans="11:14">
       <c r="M7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N7" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="11:14">
       <c r="M8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N8" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="11:14">
       <c r="M9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N9" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="11:14">
       <c r="M10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N10" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="11:14">
       <c r="M11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N11" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="11:14">
       <c r="M12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N12" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="11:14">
       <c r="M13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N13" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="11:14">
       <c r="M14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N14" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="11:14">
       <c r="M15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="11:14">
       <c r="M16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="13:13">
       <c r="M17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="13:13">
       <c r="M18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="13:13">
       <c r="M19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="13:13">
       <c r="M20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="13:13">
       <c r="M21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" spans="13:13">
       <c r="M22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="13:13">
       <c r="M23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="13:13">
       <c r="M24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="13:13">
       <c r="M25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="13:13">
       <c r="M26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="13:13">
       <c r="M27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="13:13">
       <c r="M28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="13:13">
       <c r="M29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="13:13">
       <c r="M30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="13:13">
       <c r="M31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="13:13">
       <c r="M32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" spans="13:13">
       <c r="M33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="13:13">
       <c r="M34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="13:13">
       <c r="M35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="13:13">
       <c r="M36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="13:13">
       <c r="M37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="13:13">
       <c r="M38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="13:13">
       <c r="M39" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="13:13">
       <c r="M40" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="13:13">
       <c r="M41" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" spans="13:13">
       <c r="M42" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" spans="13:13">
       <c r="M43" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" spans="13:13">
       <c r="M44" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45" spans="13:13">
       <c r="M45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="13:13">
       <c r="M46" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="13:13">
       <c r="M47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="13:13">
       <c r="M48" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="49" spans="13:13">
       <c r="M49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="13:13">
       <c r="M50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="51" spans="13:13">
       <c r="M51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52" spans="13:13">
       <c r="M52" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="13:13">
       <c r="M53" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="13:13">
       <c r="M54" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="13:13">
       <c r="M55" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="56" spans="13:13">
       <c r="M56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="13:13">
       <c r="M57" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58" spans="13:13">
       <c r="M58" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="13:13">
       <c r="M59" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="13:13">
       <c r="M60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="13:13">
       <c r="M61" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="13:13">
       <c r="M62" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="63" spans="13:13">
       <c r="M63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="64" spans="13:13">
       <c r="M64" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="13:13">
       <c r="M65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="66" spans="13:13">
       <c r="M66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="13:13">
       <c r="M67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="68" spans="13:13">
       <c r="M68" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" spans="13:13">
       <c r="M69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" spans="13:13">
       <c r="M70" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="13:13">
       <c r="M71" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="72" spans="13:13">
       <c r="M72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" spans="13:13">
       <c r="M73" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="13:13">
       <c r="M74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="75" spans="13:13">
       <c r="M75" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="13:13">
       <c r="M76" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="77" spans="13:13">
       <c r="M77" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" spans="13:13">
       <c r="M78" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="13:13">
       <c r="M79" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="80" spans="13:13">
       <c r="M80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="81" spans="13:13">
       <c r="M81" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="82" spans="13:13">
       <c r="M82" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="13:13">
       <c r="M83" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="13:13">
       <c r="M84" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="13:13">
       <c r="M85" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="86" spans="13:13">
       <c r="M86" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="87" spans="13:13">
       <c r="M87" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="88" spans="13:13">
       <c r="M88" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="13:13">
       <c r="M89" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="13:13">
       <c r="M90" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="13:13">
       <c r="M91" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" spans="13:13">
       <c r="M92" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="93" spans="13:13">
       <c r="M93" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="94" spans="13:13">
       <c r="M94" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="13:13">
       <c r="M95" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="96" spans="13:13">
       <c r="M96" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="13:13">
       <c r="M97" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="13:13">
       <c r="M98" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="13:13">
       <c r="M99" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="13:13">
       <c r="M100" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" spans="13:13">
       <c r="M101" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="102" spans="13:13">
       <c r="M102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="13:13">
       <c r="M103" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="104" spans="13:13">
       <c r="M104" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="13:13">
       <c r="M105" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="13:13">
       <c r="M106" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="107" spans="13:13">
       <c r="M107" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="108" spans="13:13">
       <c r="M108" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" spans="13:13">
       <c r="M109" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="13:13">
       <c r="M110" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="111" spans="13:13">
       <c r="M111" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" spans="13:13">
       <c r="M112" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="13:13">
       <c r="M113" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="13:13">
       <c r="M114" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="13:13">
       <c r="M115" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" spans="13:13">
       <c r="M116" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="13:13">
       <c r="M117" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="118" spans="13:13">
       <c r="M118" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" spans="13:13">
       <c r="M119" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="120" spans="13:13">
       <c r="M120" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="121" spans="13:13">
       <c r="M121" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="122" spans="13:13">
       <c r="M122" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="123" spans="13:13">
       <c r="M123" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="124" spans="13:13">
       <c r="M124" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="125" spans="13:13">
       <c r="M125" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="126" spans="13:13">
       <c r="M126" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="127" spans="13:13">
       <c r="M127" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="128" spans="13:13">
       <c r="M128" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="129" spans="13:13">
       <c r="M129" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="130" spans="13:13">
       <c r="M130" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="131" spans="13:13">
       <c r="M131" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="132" spans="13:13">
       <c r="M132" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="133" spans="13:13">
       <c r="M133" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="13:13">
       <c r="M134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="135" spans="13:13">
       <c r="M135" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136" spans="13:13">
       <c r="M136" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="137" spans="13:13">
       <c r="M137" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="138" spans="13:13">
       <c r="M138" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="139" spans="13:13">
       <c r="M139" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="140" spans="13:13">
       <c r="M140" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="141" spans="13:13">
       <c r="M141" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="142" spans="13:13">
       <c r="M142" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="143" spans="13:13">
       <c r="M143" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="144" spans="13:13">
       <c r="M144" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="145" spans="13:13">
       <c r="M145" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="146" spans="13:13">
       <c r="M146" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="147" spans="13:13">
       <c r="M147" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="148" spans="13:13">
       <c r="M148" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="149" spans="13:13">
       <c r="M149" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="150" spans="13:13">
       <c r="M150" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="151" spans="13:13">
       <c r="M151" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="152" spans="13:13">
       <c r="M152" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="153" spans="13:13">
       <c r="M153" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="154" spans="13:13">
       <c r="M154" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="155" spans="13:13">
       <c r="M155" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="156" spans="13:13">
       <c r="M156" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="157" spans="13:13">
       <c r="M157" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="158" spans="13:13">
       <c r="M158" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="159" spans="13:13">
       <c r="M159" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="160" spans="13:13">
       <c r="M160" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="161" spans="13:13">
       <c r="M161" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="162" spans="13:13">
       <c r="M162" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="163" spans="13:13">
       <c r="M163" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="164" spans="13:13">
       <c r="M164" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="165" spans="13:13">
       <c r="M165" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="166" spans="13:13">
       <c r="M166" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="167" spans="13:13">
       <c r="M167" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="168" spans="13:13">
       <c r="M168" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="169" spans="13:13">
       <c r="M169" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="170" spans="13:13">
       <c r="M170" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="171" spans="13:13">
       <c r="M171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="172" spans="13:13">
       <c r="M172" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="173" spans="13:13">
       <c r="M173" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="174" spans="13:13">
       <c r="M174" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="175" spans="13:13">
       <c r="M175" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="176" spans="13:13">
       <c r="M176" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="177" spans="13:13">
       <c r="M177" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" spans="13:13">
       <c r="M178" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="179" spans="13:13">
       <c r="M179" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="180" spans="13:13">
       <c r="M180" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="181" spans="13:13">
       <c r="M181" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="182" spans="13:13">
       <c r="M182" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="183" spans="13:13">
       <c r="M183" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="184" spans="13:13">
       <c r="M184" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="185" spans="13:13">
       <c r="M185" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="186" spans="13:13">
       <c r="M186" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="187" spans="13:13">
       <c r="M187" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="188" spans="13:13">
       <c r="M188" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="189" spans="13:13">
       <c r="M189" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="190" spans="13:13">
       <c r="M190" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="191" spans="13:13">
       <c r="M191" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="192" spans="13:13">
       <c r="M192" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="193" spans="13:13">
       <c r="M193" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="194" spans="13:13">
       <c r="M194" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="195" spans="13:13">
       <c r="M195" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="196" spans="13:13">
       <c r="M196" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="197" spans="13:13">
       <c r="M197" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="198" spans="13:13">
       <c r="M198" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="199" spans="13:13">
       <c r="M199" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="200" spans="13:13">
       <c r="M200" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="201" spans="13:13">
       <c r="M201" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="202" spans="13:13">
       <c r="M202" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="203" spans="13:13">
       <c r="M203" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="204" spans="13:13">
       <c r="M204" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="205" spans="13:13">
       <c r="M205" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="206" spans="13:13">
       <c r="M206" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="207" spans="13:13">
       <c r="M207" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="208" spans="13:13">
       <c r="M208" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="209" spans="13:13">
       <c r="M209" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="210" spans="13:13">
       <c r="M210" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="211" spans="13:13">
       <c r="M211" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="212" spans="13:13">
       <c r="M212" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="213" spans="13:13">
       <c r="M213" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="214" spans="13:13">
       <c r="M214" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="215" spans="13:13">
       <c r="M215" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="216" spans="13:13">
       <c r="M216" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="217" spans="13:13">
       <c r="M217" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="218" spans="13:13">
       <c r="M218" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="219" spans="13:13">
       <c r="M219" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="220" spans="13:13">
       <c r="M220" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="221" spans="13:13">
       <c r="M221" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="222" spans="13:13">
       <c r="M222" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="223" spans="13:13">
       <c r="M223" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="224" spans="13:13">
       <c r="M224" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="225" spans="13:13">
       <c r="M225" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="226" spans="13:13">
       <c r="M226" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="227" spans="13:13">
       <c r="M227" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="228" spans="13:13">
       <c r="M228" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="229" spans="13:13">
       <c r="M229" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="230" spans="13:13">
       <c r="M230" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="231" spans="13:13">
       <c r="M231" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="232" spans="13:13">
       <c r="M232" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="233" spans="13:13">
       <c r="M233" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="234" spans="13:13">
       <c r="M234" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="235" spans="13:13">
       <c r="M235" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="236" spans="13:13">
       <c r="M236" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="237" spans="13:13">
       <c r="M237" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="238" spans="13:13">
       <c r="M238" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="239" spans="13:13">
       <c r="M239" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="240" spans="13:13">
       <c r="M240" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="241" spans="13:13">
       <c r="M241" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="242" spans="13:13">
       <c r="M242" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="243" spans="13:13">
       <c r="M243" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="244" spans="13:13">
       <c r="M244" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="245" spans="13:13">
       <c r="M245" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="246" spans="13:13">
       <c r="M246" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="247" spans="13:13">
       <c r="M247" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="248" spans="13:13">
       <c r="M248" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="249" spans="13:13">
       <c r="M249" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="250" spans="13:13">
       <c r="M250" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="251" spans="13:13">
       <c r="M251" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="252" spans="13:13">
       <c r="M252" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="253" spans="13:13">
       <c r="M253" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="254" spans="13:13">
       <c r="M254" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="255" spans="13:13">
       <c r="M255" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="256" spans="13:13">
       <c r="M256" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="257" spans="13:13">
       <c r="M257" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="258" spans="13:13">
       <c r="M258" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="259" spans="13:13">
       <c r="M259" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="260" spans="13:13">
       <c r="M260" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="261" spans="13:13">
       <c r="M261" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="262" spans="13:13">
       <c r="M262" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="263" spans="13:13">
       <c r="M263" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="264" spans="13:13">
       <c r="M264" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="265" spans="13:13">
       <c r="M265" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="266" spans="13:13">
       <c r="M266" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="267" spans="13:13">
       <c r="M267" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="268" spans="13:13">
       <c r="M268" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="269" spans="13:13">
       <c r="M269" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="270" spans="13:13">
       <c r="M270" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="271" spans="13:13">
       <c r="M271" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="272" spans="13:13">
       <c r="M272" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="273" spans="13:13">
       <c r="M273" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="274" spans="13:13">
       <c r="M274" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="275" spans="13:13">
       <c r="M275" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="276" spans="13:13">
       <c r="M276" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="277" spans="13:13">
       <c r="M277" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="278" spans="13:13">
       <c r="M278" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="279" spans="13:13">
       <c r="M279" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="280" spans="13:13">
       <c r="M280" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="281" spans="13:13">
       <c r="M281" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="282" spans="13:13">
       <c r="M282" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="283" spans="13:13">
       <c r="M283" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="284" spans="13:13">
       <c r="M284" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="285" spans="13:13">
       <c r="M285" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="286" spans="13:13">
       <c r="M286" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="287" spans="13:13">
       <c r="M287" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="288" spans="13:13">
       <c r="M288" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="289" spans="13:13">
       <c r="M289" t="s">
-        <v>575</v>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="290" spans="13:13">
+      <c r="M290" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="291" spans="13:13">
+      <c r="M291" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="292" spans="13:13">
+      <c r="M292" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="293" spans="13:13">
+      <c r="M293" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="294" spans="13:13">
+      <c r="M294" t="s">
+        <v>581</v>
       </c>
     </row>
   </sheetData>
